--- a/data/summer-research/review/summer_research_catalog_review.xlsx
+++ b/data/summer-research/review/summer_research_catalog_review.xlsx
@@ -277,8 +277,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="SourcesTable" displayName="SourcesTable" ref="A1:F35" headerRowCount="1">
-  <autoFilter ref="A1:F35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="SourcesTable" displayName="SourcesTable" ref="A1:F42" headerRowCount="1">
+  <autoFilter ref="A1:F42"/>
   <tableColumns count="6">
     <tableColumn id="1" name="source_id"/>
     <tableColumn id="2" name="source_url"/>
@@ -292,8 +292,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="VerificationsTable" displayName="VerificationsTable" ref="A1:K57" headerRowCount="1">
-  <autoFilter ref="A1:K57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="VerificationsTable" displayName="VerificationsTable" ref="A1:K90" headerRowCount="1">
+  <autoFilter ref="A1:K90"/>
   <tableColumns count="11">
     <tableColumn id="1" name="verification_id"/>
     <tableColumn id="2" name="opportunity_id"/>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AK2" s="2" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
@@ -1094,15 +1094,19 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>See current SSRP-Amgen eligibility</t>
+          <t>U.S. citizen or permanent resident</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Undergraduate; current program requirements apply</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
+          <t>Four-year college; sophomore/junior/non-graduating senior</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>8.0</t>
@@ -1196,7 +1200,7 @@
       </c>
       <c r="AJ3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AK3" s="2" t="inlineStr">
@@ -1206,7 +1210,7 @@
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
@@ -1389,7 +1393,7 @@
       </c>
       <c r="AJ4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AK4" s="2" t="inlineStr">
@@ -1399,7 +1403,7 @@
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
@@ -1592,7 +1596,7 @@
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
@@ -1769,7 +1773,7 @@
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM6" s="2" t="inlineStr">
@@ -1954,7 +1958,7 @@
       </c>
       <c r="AL7" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM7" s="2" t="inlineStr">
@@ -2139,7 +2143,7 @@
       </c>
       <c r="AL8" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM8" s="2" t="inlineStr">
@@ -2312,7 +2316,7 @@
       </c>
       <c r="AL9" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM9" s="2" t="inlineStr">
@@ -2501,7 +2505,7 @@
       </c>
       <c r="AL10" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM10" s="2" t="inlineStr">
@@ -2690,7 +2694,7 @@
       </c>
       <c r="AL11" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM11" s="2" t="inlineStr">
@@ -2867,7 +2871,7 @@
       </c>
       <c r="AL12" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM12" s="2" t="inlineStr">
@@ -3052,7 +3056,7 @@
       </c>
       <c r="AL13" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM13" s="2" t="inlineStr">
@@ -3233,7 +3237,7 @@
       </c>
       <c r="AL14" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM14" s="2" t="inlineStr">
@@ -3410,7 +3414,7 @@
       </c>
       <c r="AL15" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM15" s="2" t="inlineStr">
@@ -3603,7 +3607,7 @@
       </c>
       <c r="AL16" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM16" s="2" t="inlineStr">
@@ -3776,7 +3780,7 @@
       </c>
       <c r="AL17" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM17" s="2" t="inlineStr">
@@ -3953,7 +3957,7 @@
       </c>
       <c r="AL18" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM18" s="2" t="inlineStr">
@@ -4118,7 +4122,7 @@
       </c>
       <c r="AL19" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM19" s="2" t="inlineStr">
@@ -4303,7 +4307,7 @@
       </c>
       <c r="AL20" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM20" s="2" t="inlineStr">
@@ -4480,7 +4484,7 @@
       </c>
       <c r="AL21" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM21" s="2" t="inlineStr">
@@ -4669,7 +4673,7 @@
       </c>
       <c r="AL22" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM22" s="2" t="inlineStr">
@@ -4862,7 +4866,7 @@
       </c>
       <c r="AL23" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM23" s="2" t="inlineStr">
@@ -5055,7 +5059,7 @@
       </c>
       <c r="AL24" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM24" s="2" t="inlineStr">
@@ -5248,7 +5252,7 @@
       </c>
       <c r="AL25" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM25" s="2" t="inlineStr">
@@ -5425,7 +5429,7 @@
       </c>
       <c r="AL26" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM26" s="2" t="inlineStr">
@@ -5618,7 +5622,7 @@
       </c>
       <c r="AL27" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM27" s="2" t="inlineStr">
@@ -5811,7 +5815,7 @@
       </c>
       <c r="AL28" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM28" s="2" t="inlineStr">
@@ -6004,7 +6008,7 @@
       </c>
       <c r="AL29" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM29" s="2" t="inlineStr">
@@ -6197,7 +6201,7 @@
       </c>
       <c r="AL30" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM30" s="2" t="inlineStr">
@@ -6390,7 +6394,7 @@
       </c>
       <c r="AL31" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM31" s="2" t="inlineStr">
@@ -6583,7 +6587,7 @@
       </c>
       <c r="AL32" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM32" s="2" t="inlineStr">
@@ -6776,7 +6780,7 @@
       </c>
       <c r="AL33" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM33" s="2" t="inlineStr">
@@ -6953,7 +6957,7 @@
       </c>
       <c r="AL34" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM34" s="2" t="inlineStr">
@@ -7134,7 +7138,7 @@
       </c>
       <c r="AL35" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM35" s="2" t="inlineStr">
@@ -7327,7 +7331,7 @@
       </c>
       <c r="AL36" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="AM36" s="2" t="inlineStr">
@@ -11868,7 +11872,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -11981,7 +11985,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -12086,7 +12090,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -12563,14 +12567,14 @@
     <col width="28" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="19" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
     <col width="28" customWidth="1" min="17" max="17"/>
     <col width="31" customWidth="1" min="18" max="18"/>
     <col width="32" customWidth="1" min="19" max="19"/>
     <col width="25" customWidth="1" min="20" max="20"/>
     <col width="23" customWidth="1" min="21" max="21"/>
     <col width="34" customWidth="1" min="22" max="22"/>
-    <col width="17" customWidth="1" min="23" max="23"/>
+    <col width="34" customWidth="1" min="23" max="23"/>
     <col width="14" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
@@ -12717,30 +12721,74 @@
           <t>U.S. citizen or permanent resident</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>At least one undergraduate semester must remain after the summer experience.</t>
+        </is>
+      </c>
       <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr"/>
       <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -12748,13 +12796,17 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen or permanent resident | Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
+          <t>U.S. citizen or permanent resident; enrolled in a degree-granting program at a U.S. or territorial college or university; cumulative GPA 3.0 or higher; at least two semesters completed by summer and at least one semester remaining afterward; strong interest in a Ph.D.</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>At least two undergraduate semesters completed by summer; GPA &gt;= 3.0; committed interest in Ph.D. study; full-time participation required.</t>
+        </is>
+      </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -12779,30 +12831,74 @@
           <t>U.S. citizen or permanent resident</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>At least one undergraduate semester must remain after the summer experience.</t>
+        </is>
+      </c>
       <c r="Q3" s="2" t="inlineStr"/>
       <c r="R3" s="2" t="inlineStr"/>
       <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -12810,13 +12906,17 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen or permanent resident | Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr"/>
+          <t>U.S. citizen or permanent resident; enrolled in a degree-granting program at a U.S. or territorial college or university; cumulative GPA 3.0 or higher; at least two semesters completed by summer and at least one semester remaining afterward; strong interest in a Ph.D.</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>At least two undergraduate semesters completed by summer; GPA &gt;= 3.0; committed interest in Ph.D. study; full-time participation required.</t>
+        </is>
+      </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -12841,30 +12941,74 @@
           <t>U.S. citizen or permanent resident</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>At least one undergraduate semester must remain after the summer experience.</t>
+        </is>
+      </c>
       <c r="Q4" s="2" t="inlineStr"/>
       <c r="R4" s="2" t="inlineStr"/>
       <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -12872,13 +13016,17 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen or permanent resident | Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr"/>
+          <t>U.S. citizen or permanent resident; enrolled in a degree-granting program at a U.S. or territorial college or university; cumulative GPA 3.0 or higher; at least two semesters completed by summer and at least one semester remaining afterward; strong interest in a Ph.D.</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>At least two undergraduate semesters completed by summer; GPA &gt;= 3.0; committed interest in Ph.D. study; full-time participation required.</t>
+        </is>
+      </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -12903,30 +13051,74 @@
           <t>U.S. citizen or permanent resident</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>At least one undergraduate semester must remain after the summer experience.</t>
+        </is>
+      </c>
       <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="inlineStr"/>
       <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -12934,13 +13126,17 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen or permanent resident | Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr"/>
+          <t>U.S. citizen or permanent resident; enrolled in a degree-granting program at a U.S. or territorial college or university; cumulative GPA 3.0 or higher; at least two semesters completed by summer and at least one semester remaining afterward; strong interest in a Ph.D.</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>At least two undergraduate semesters completed by summer; GPA &gt;= 3.0; committed interest in Ph.D. study; full-time participation required.</t>
+        </is>
+      </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -12965,30 +13161,74 @@
           <t>U.S. citizen or permanent resident</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>At least one undergraduate semester must remain after the summer experience.</t>
+        </is>
+      </c>
       <c r="Q6" s="2" t="inlineStr"/>
       <c r="R6" s="2" t="inlineStr"/>
       <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -12996,13 +13236,17 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen or permanent resident | Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr"/>
+          <t>U.S. citizen or permanent resident; enrolled in a degree-granting program at a U.S. or territorial college or university; cumulative GPA 3.0 or higher; at least two semesters completed by summer and at least one semester remaining afterward; strong interest in a Ph.D.</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>At least two undergraduate semesters completed by summer; GPA &gt;= 3.0; committed interest in Ph.D. study; full-time participation required.</t>
+        </is>
+      </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -13027,30 +13271,74 @@
           <t>U.S. citizen or permanent resident</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>At least one undergraduate semester must remain after the summer experience.</t>
+        </is>
+      </c>
       <c r="Q7" s="2" t="inlineStr"/>
       <c r="R7" s="2" t="inlineStr"/>
       <c r="S7" s="2" t="inlineStr"/>
-      <c r="T7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -13058,13 +13346,17 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen or permanent resident | Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr"/>
+          <t>U.S. citizen or permanent resident; enrolled in a degree-granting program at a U.S. or territorial college or university; cumulative GPA 3.0 or higher; at least two semesters completed by summer and at least one semester remaining afterward; strong interest in a Ph.D.</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>At least two undergraduate semesters completed by summer; GPA &gt;= 3.0; committed interest in Ph.D. study; full-time participation required.</t>
+        </is>
+      </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -13089,30 +13381,74 @@
           <t>U.S. citizen or permanent resident</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>At least one undergraduate semester must remain after the summer experience.</t>
+        </is>
+      </c>
       <c r="Q8" s="2" t="inlineStr"/>
       <c r="R8" s="2" t="inlineStr"/>
       <c r="S8" s="2" t="inlineStr"/>
-      <c r="T8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -13120,13 +13456,17 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen or permanent resident | Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr"/>
+          <t>U.S. citizen or permanent resident; enrolled in a degree-granting program at a U.S. or territorial college or university; cumulative GPA 3.0 or higher; at least two semesters completed by summer and at least one semester remaining afterward; strong interest in a Ph.D.</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>At least two undergraduate semesters completed by summer; GPA &gt;= 3.0; committed interest in Ph.D. study; full-time participation required.</t>
+        </is>
+      </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -13151,30 +13491,74 @@
           <t>U.S. citizen or permanent resident</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>At least one undergraduate semester must remain after the summer experience.</t>
+        </is>
+      </c>
       <c r="Q9" s="2" t="inlineStr"/>
       <c r="R9" s="2" t="inlineStr"/>
       <c r="S9" s="2" t="inlineStr"/>
-      <c r="T9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -13182,13 +13566,17 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen or permanent resident | Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr"/>
+          <t>U.S. citizen or permanent resident; enrolled in a degree-granting program at a U.S. or territorial college or university; cumulative GPA 3.0 or higher; at least two semesters completed by summer and at least one semester remaining afterward; strong interest in a Ph.D.</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>At least two undergraduate semesters completed by summer; GPA &gt;= 3.0; committed interest in Ph.D. study; full-time participation required.</t>
+        </is>
+      </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -13213,30 +13601,74 @@
           <t>U.S. citizen or permanent resident</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>At least one undergraduate semester must remain after the summer experience.</t>
+        </is>
+      </c>
       <c r="Q10" s="2" t="inlineStr"/>
       <c r="R10" s="2" t="inlineStr"/>
       <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -13244,13 +13676,17 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen or permanent resident | Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr"/>
+          <t>U.S. citizen or permanent resident; enrolled in a degree-granting program at a U.S. or territorial college or university; cumulative GPA 3.0 or higher; at least two semesters completed by summer and at least one semester remaining afterward; strong interest in a Ph.D.</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>At least two undergraduate semesters completed by summer; GPA &gt;= 3.0; committed interest in Ph.D. study; full-time participation required.</t>
+        </is>
+      </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -13275,30 +13711,74 @@
           <t>U.S. citizen or permanent resident</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>At least one undergraduate semester must remain after the summer experience.</t>
+        </is>
+      </c>
       <c r="Q11" s="2" t="inlineStr"/>
       <c r="R11" s="2" t="inlineStr"/>
       <c r="S11" s="2" t="inlineStr"/>
-      <c r="T11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -13306,13 +13786,17 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen or permanent resident | Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr"/>
+          <t>U.S. citizen or permanent resident; enrolled in a degree-granting program at a U.S. or territorial college or university; cumulative GPA 3.0 or higher; at least two semesters completed by summer and at least one semester remaining afterward; strong interest in a Ph.D.</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>At least two undergraduate semesters completed by summer; GPA &gt;= 3.0; committed interest in Ph.D. study; full-time participation required.</t>
+        </is>
+      </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -13337,30 +13821,74 @@
           <t>U.S. citizen or permanent resident</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>At least one undergraduate semester must remain after the summer experience.</t>
+        </is>
+      </c>
       <c r="Q12" s="2" t="inlineStr"/>
       <c r="R12" s="2" t="inlineStr"/>
       <c r="S12" s="2" t="inlineStr"/>
-      <c r="T12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -13368,13 +13896,17 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen or permanent resident | Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr"/>
+          <t>U.S. citizen or permanent resident; enrolled in a degree-granting program at a U.S. or territorial college or university; cumulative GPA 3.0 or higher; at least two semesters completed by summer and at least one semester remaining afterward; strong interest in a Ph.D.</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>At least two undergraduate semesters completed by summer; GPA &gt;= 3.0; committed interest in Ph.D. study; full-time participation required.</t>
+        </is>
+      </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -13399,30 +13931,74 @@
           <t>U.S. citizen or permanent resident</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>At least one undergraduate semester must remain after the summer experience.</t>
+        </is>
+      </c>
       <c r="Q13" s="2" t="inlineStr"/>
       <c r="R13" s="2" t="inlineStr"/>
       <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -13430,13 +14006,17 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen or permanent resident | Undergraduate; ≥2 semesters completed; ≥1 semester remaining after summer</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr"/>
+          <t>U.S. citizen or permanent resident; enrolled in a degree-granting program at a U.S. or territorial college or university; cumulative GPA 3.0 or higher; at least two semesters completed by summer and at least one semester remaining afterward; strong interest in a Ph.D.</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>At least two undergraduate semesters completed by summer; GPA &gt;= 3.0; committed interest in Ph.D. study; full-time participation required.</t>
+        </is>
+      </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -13461,29 +14041,77 @@
           <t>U.S. citizen or lawful permanent resident</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Undergraduates and qualifying recent graduates; see DOE eligibility rules</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Associate's, bachelor's, and combined BS/MS graduates may qualify when the degree-to-start interval is no more than two years.</t>
+        </is>
+      </c>
       <c r="Q14" s="2" t="inlineStr"/>
-      <c r="R14" s="2" t="inlineStr"/>
-      <c r="S14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="T14" s="2" t="inlineStr"/>
       <c r="U14" s="2" t="inlineStr">
         <is>
@@ -13492,13 +14120,17 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen or lawful permanent resident | Undergraduates and qualifying recent graduates; see DOE eligibility rules</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr"/>
+          <t>U.S. citizen or lawful permanent resident; age 18 or older; full-time undergraduate at an accredited community, two-year, or four-year institution with at least one matriculated semester, 6 STEM credits, 12 total credits, and cumulative GPA 3.0; qualifying recent graduates within two years are also eligible.</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>Age &gt;= 18; at least one matriculated semester; &gt;= 6 STEM and &gt;= 12 total undergraduate credits; GPA &gt;= 3.0; participation and application limits apply.</t>
+        </is>
+      </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -13523,25 +14155,73 @@
           <t>U.S. citizen or permanent resident</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>College, graduate, and professional students; undergraduates eligible</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Graduating undergraduates may qualify when accepted into an accredited graduate program for fall.</t>
+        </is>
+      </c>
       <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="T15" s="2" t="inlineStr"/>
       <c r="U15" s="2" t="inlineStr">
         <is>
@@ -13550,13 +14230,17 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen or permanent resident | College, graduate, and professional students; undergraduates eligible</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr"/>
+          <t>U.S. citizen or permanent resident; at least age 18 by the stated cycle date, with a limited nearby-campus exception for some graduating high-school seniors; enrolled at least half-time in an accredited community college, college, university, graduate, or professional program, or accepted into an accredited graduate program for fall.</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>Permanent residents must attend or be accepted by a U.S. educational institution; full-time summer research schedule.</t>
+        </is>
+      </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -13581,30 +14265,74 @@
           <t>U.S. citizen</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>College students; project-specific requirements</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Recent graduates may apply for the three internship sessions immediately following graduation.</t>
+        </is>
+      </c>
       <c r="Q16" s="2" t="inlineStr"/>
       <c r="R16" s="2" t="inlineStr"/>
       <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -13612,13 +14340,17 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen | College students; project-specific requirements</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr"/>
+          <t>U.S. citizen; cumulative GPA 3.0; at least age 16; full- or part-time college student in a degree-granting program at a U.S. Department of Education accredited institution. Recent graduates may apply for internships in the three sessions immediately following graduation.</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>Age &gt;= 16; GPA &gt;= 3.0; course of study must align with NASA needs.</t>
+        </is>
+      </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -13643,25 +14375,69 @@
           <t>See NIST cycle eligibility</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Undergraduate; cycle-specific</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
-      <c r="S17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
@@ -13670,13 +14446,17 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Yes | See NIST cycle eligibility | Undergraduate; cycle-specific</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr"/>
+          <t>U.S. citizen or permanent resident; full-time undergraduate at an accredited U.S. two-year or four-year college; first-year undergraduates and graduating seniors are eligible; age 18 or older; background check and health insurance required.</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>Age &gt;= 18; background check, health insurance, direct deposit, and full-time participation required.</t>
+        </is>
+      </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -13701,21 +14481,57 @@
           <t>U.S. citizen; permanent residents considered at some labs</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Sophomore, junior, senior, and graduate students in relevant majors</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr"/>
       <c r="R18" s="2" t="inlineStr"/>
@@ -13728,13 +14544,17 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen; permanent residents considered at some labs | Sophomore, junior, senior, and graduate students in relevant majors</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr"/>
+          <t>U.S. citizen, with permanent resident status considered at some laboratories; sophomore, junior, senior, or graduate student enrolled at a participating university in a major relevant to participating laboratory research.</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>Permanent-resident eligibility is laboratory-specific; new undergraduate stipend tier expects at least 31 credits by the end of spring.</t>
+        </is>
+      </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -13759,26 +14579,74 @@
           <t>Enrollment-based eligibility; applicants from eligible North American/British/Irish universities</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Undergraduates in qualifying degree programs; generally ≥2 years completed by internship</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Must maintain undergraduate status after the internship.</t>
+        </is>
+      </c>
       <c r="Q19" s="2" t="inlineStr"/>
       <c r="R19" s="2" t="inlineStr"/>
-      <c r="S19" s="2" t="inlineStr"/>
-      <c r="T19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -13786,13 +14654,17 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Yes | Enrollment-based eligibility; applicants from eligible North American/British/Irish universities | Undergraduates in qualifying degree programs; generally ≥2 years completed by internship</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr"/>
+          <t>Undergraduate in a four-year program at a U.S., Canadian, U.K., or Irish institution in an eligible field; at least two years of the degree completed by the internship; must retain undergraduate status afterward. International students must have studied at an eligible institution for more than 12 months by the deadline.</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>Eligible institution countries and fields apply; international students need &gt;12 months at an eligible institution; special six-year residence rule for German citizens.</t>
+        </is>
+      </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -13817,26 +14689,70 @@
           <t>See current Leadership Alliance eligibility</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Undergraduates; host and program rules apply</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>At least one undergraduate semester must remain at the start of the summer program.</t>
+        </is>
+      </c>
       <c r="Q20" s="2" t="inlineStr"/>
       <c r="R20" s="2" t="inlineStr"/>
       <c r="S20" s="2" t="inlineStr"/>
-      <c r="T20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -13844,13 +14760,17 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Yes | See current Leadership Alliance eligibility | Undergraduates; host and program rules apply</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr"/>
+          <t>Documented U.S. citizen, non-citizen national, or permanent resident; full-time enrollment at an accredited U.S. or territorial college or university; GPA 3.0 or better; at least two semesters completed and one undergraduate semester remaining by summer; committed interest in Ph.D. or MD-Ph.D. study.</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>GPA &gt;= 3.0; intended for Ph.D. or MD-Ph.D., not professional-practice degrees.</t>
+        </is>
+      </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -13875,40 +14795,88 @@
           <t>U.S. citizen or permanent resident</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Four-year college students enrolled the following fall; preference for sophomores/juniors</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Must be enrolled in a four-year college in the fall after the program; graduating seniors are ineligible.</t>
+        </is>
+      </c>
       <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
-      <c r="S21" s="2" t="inlineStr"/>
-      <c r="T21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen or permanent resident | Four-year college students enrolled the following fall; preference for sophomores/juniors</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr"/>
+          <t>U.S. citizen or permanent resident; enrolled in a four-year college for the fall after the program; graduating seniors ineligible. Prior research is not required, with preference for students who completed sophomore or junior year.</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>Preference, not a hard requirement, for students who completed sophomore or junior year; full 10-week commitment.</t>
+        </is>
+      </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -13933,21 +14901,57 @@
           <t>International students eligible; see current application rules</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>College sophomores and juniors</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr"/>
       <c r="R22" s="2" t="inlineStr"/>
@@ -13955,18 +14959,18 @@
       <c r="T22" s="2" t="inlineStr"/>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Yes | International students eligible; see current application rules | College sophomores and juniors</t>
+          <t>College sophomores and juniors in the life or physical sciences; international students are eligible.</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr"/>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -13991,40 +14995,88 @@
           <t>Students worldwide eligible</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Undergraduates; current eligibility rules apply</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr"/>
-      <c r="O23" s="2" t="inlineStr"/>
-      <c r="P23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>Must return to an undergraduate degree program after summer.</t>
+        </is>
+      </c>
       <c r="Q23" s="2" t="inlineStr"/>
       <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="inlineStr"/>
-      <c r="T23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Yes | Students worldwide eligible | Undergraduates; current eligibility rules apply</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr"/>
+          <t>Current sophomores and juniors are eligible; exceptional first-year students with prior independent research may be considered; participants must return to an undergraduate degree program after summer. Students of any nationality may apply, subject to stated U.S.-institution or partner-institution rules for international students.</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>First-year eligibility is exceptional and requires prior independent research; international eligibility depends on institution/partner conditions.</t>
+        </is>
+      </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -14049,22 +15101,62 @@
           <t>U.S. citizen or permanent resident</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Students entering final undergraduate year after the summer</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>Must enter the final undergraduate year or academic term after the summer program.</t>
+        </is>
+      </c>
       <c r="Q24" s="2" t="inlineStr"/>
       <c r="R24" s="2" t="inlineStr"/>
       <c r="S24" s="2" t="inlineStr"/>
@@ -14076,13 +15168,13 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen or permanent resident | Students entering final undergraduate year after the summer</t>
+          <t>U.S. citizen or permanent resident; enrolled undergraduate entering the final year or semester/quarter of study after summer.</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr"/>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -14109,38 +15201,78 @@
       </c>
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Early undergraduates; designed for students not yet entering third year and with limited research experience</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr"/>
-      <c r="O25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr"/>
-      <c r="R25" s="2" t="inlineStr"/>
-      <c r="S25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="T25" s="2" t="inlineStr"/>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Yes | See current program eligibility | Early undergraduates; designed for students not yet entering third year and with limited research experience</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr"/>
+          <t>Must have graduated high school, not yet entered the third undergraduate year, and be enrolled or planning to enroll in a two- or four-year institution; age 16 or older. International students are not accepted. Prior research is not required.</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>Age &gt;= 16; applicants must not yet have entered their third undergraduate year.</t>
+        </is>
+      </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -14167,38 +15299,78 @@
       </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Undergraduates at 2- or 4-year colleges; see cycle rules</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr"/>
-      <c r="R26" s="2" t="inlineStr"/>
-      <c r="S26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="T26" s="2" t="inlineStr"/>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Yes | International students not eligible for 2026 program | Undergraduates at 2- or 4-year colleges; see cycle rules</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr"/>
+          <t>Incoming or current undergraduate enrolled or planning to enroll in a two- or four-year institution; age 18 or older. International students are not accepted. No prior research experience is required.</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>Age &gt;= 18.</t>
+        </is>
+      </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -14232,16 +15404,32 @@
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P27" s="2" t="inlineStr"/>
       <c r="Q27" s="2" t="inlineStr"/>
       <c r="R27" s="2" t="inlineStr"/>
@@ -14254,13 +15442,17 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen or permanent resident | Non-BU rising sophomores/juniors/seniors; some tracks emphasize rising juniors/seniors</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr"/>
+          <t>Non-Boston University undergraduates who will be rising juniors or rising seniors are eligible for the described SURF tracks.</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>Class-year booleans use application-time standing: rising junior corresponds to current sophomore and rising senior to current junior; BU students are ineligible.</t>
+        </is>
+      </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -14285,9 +15477,21 @@
           <t>NSF REU eligibility typically U.S. citizen/PR; verify current cycle</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Undergraduate; non-BU students</t>
@@ -14299,7 +15503,11 @@
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr"/>
       <c r="R28" s="2" t="inlineStr"/>
@@ -14312,13 +15520,17 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Yes | NSF REU eligibility typically U.S. citizen/PR; verify current cycle | Undergraduate; non-BU students</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr"/>
+          <t>Non-Boston University undergraduate students; U.S. citizen or permanent resident.</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>Boston University students are ineligible; official page does not state hard class-year, GPA, or prior-research requirements.</t>
+        </is>
+      </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -14343,40 +15555,92 @@
           <t>U.S. citizen or permanent resident</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t>STEM majors at 2- and 4-year colleges; non-BU students</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr"/>
-      <c r="P29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>Must not graduate before December of the program year.</t>
+        </is>
+      </c>
       <c r="Q29" s="2" t="inlineStr"/>
-      <c r="R29" s="2" t="inlineStr"/>
-      <c r="S29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="T29" s="2" t="inlineStr"/>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen or permanent resident | STEM majors at 2- and 4-year colleges; non-BU students</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr"/>
+          <t>U.S. citizen or permanent resident; STEM major at a two- or four-year college; currently enrolled undergraduate who has completed at least the first year and will not graduate before December of the program year. Boston University undergraduates are ineligible.</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>BU undergraduates are ineligible; full 10-week participation required.</t>
+        </is>
+      </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -14401,44 +15665,100 @@
           <t>U.S. citizen or permanent resident</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Four-year college; sophomore/junior/non-graduating senior</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr"/>
-      <c r="P30" s="2" t="inlineStr"/>
-      <c r="Q30" s="2" t="inlineStr"/>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>Must return in fall 2026 to continue undergraduate studies</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>Enrollment in a four-year U.S. college or university including Puerto Rico and U.S. territories</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="T30" s="2" t="inlineStr"/>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>preferred</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen or permanent resident | Four-year college; sophomore/junior/non-graduating senior</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr"/>
+          <t>U.S. citizen or permanent resident; enrolled at a four-year institution; sophomore junior or returning non-graduating senior; minimum 3.2 GPA; freshmen and community-college students ineligible</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>Previous Amgen Scholars are ineligible</t>
+        </is>
+      </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -14460,28 +15780,84 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>See current SSRP-Amgen eligibility</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
+          <t>U.S. citizen or permanent resident</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Undergraduate; current program requirements apply</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="2" t="inlineStr"/>
-      <c r="P31" s="2" t="inlineStr"/>
-      <c r="Q31" s="2" t="inlineStr"/>
-      <c r="R31" s="2" t="inlineStr"/>
-      <c r="S31" s="2" t="inlineStr"/>
+          <t>Four-year college; sophomore/junior/non-graduating senior</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>Must return in fall after SSRP to continue undergraduate studies</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>Enrollment in an accredited four-year U.S. college or university including Puerto Rico and U.S. territories</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="T31" s="2" t="inlineStr"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
@@ -14490,13 +15866,17 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Yes | See current SSRP-Amgen eligibility | Undergraduate; current program requirements apply</t>
-        </is>
-      </c>
-      <c r="W31" s="2" t="inlineStr"/>
+          <t>U.S. citizen or permanent resident; enrolled at an accredited four-year institution; sophomore junior or returning non-graduating senior; minimum 3.2 GPA</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>Interest in pursuing a Ph.D. or in exceptional cases an M.D./Ph.D.</t>
+        </is>
+      </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -14521,44 +15901,100 @@
           <t>U.S. citizen or permanent resident</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Four-year college; sophomore/junior/non-graduating senior</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr"/>
-      <c r="P32" s="2" t="inlineStr"/>
-      <c r="Q32" s="2" t="inlineStr"/>
-      <c r="R32" s="2" t="inlineStr"/>
-      <c r="S32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>Must return in fall 2026 to continue undergraduate studies</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>Enrollment in an accredited four-year U.S. college or university including Puerto Rico and U.S. territories</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="T32" s="2" t="inlineStr"/>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen or permanent resident | Four-year college; sophomore/junior/non-graduating senior</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="inlineStr"/>
+          <t>U.S. citizen or permanent resident; enrolled at an accredited four-year institution; sophomore junior or returning non-graduating senior; minimum 3.2 GPA</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>Interest in pursuing a Ph.D. or M.D./Ph.D. in biotechnology or related biomedical sciences</t>
+        </is>
+      </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -14583,40 +16019,76 @@
           <t>Primarily U.S. citizens/permanent residents; exceptions may require outside funding</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Undergraduates; see project-specific eligibility</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr"/>
       <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr"/>
-      <c r="S33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="T33" s="2" t="inlineStr"/>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Yes | Primarily U.S. citizens/permanent residents; exceptions may require outside funding | Undergraduates; see project-specific eligibility</t>
-        </is>
-      </c>
-      <c r="W33" s="2" t="inlineStr"/>
+          <t>Open to undergraduates at two- and four-year institutions; core funding is primarily for U.S. citizens and permanent residents. The official FAQ describes limited, funding-dependent exceptions for some international students and graduates. Significant prior ecological research is not required, though individual projects may add requirements.</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>International and post-graduation participation is funding-dependent and uncommon; project-specific requirements and full-program availability apply.</t>
+        </is>
+      </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -14641,40 +16113,92 @@
           <t>Foreign students may be eligible if studying in the U.S.; verify current cycle</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Undergraduates; graduating seniors may be eligible</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr"/>
-      <c r="P34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>For 2026, recent graduates with a bachelor's degree received no earlier than December 2025 were eligible.</t>
+        </is>
+      </c>
       <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="T34" s="2" t="inlineStr"/>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Yes | Foreign students may be eligible if studying in the U.S.; verify current cycle | Undergraduates; graduating seniors may be eligible</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr"/>
+          <t>Students enrolled in or just completing a bachelor's degree; recent graduates whose degree falls within the cycle's stated window are eligible. International students are eligible only when studying in the United States; foreign students at foreign institutions are not eligible. Minimum age 18.</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>International applicants must study in the U.S.; age &gt;= 18; strong mathematics background expected.</t>
+        </is>
+      </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -14699,40 +16223,84 @@
           <t>U.S. citizen or permanent resident</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Undergraduates; current REU eligibility rules apply</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr"/>
-      <c r="O35" s="2" t="inlineStr"/>
-      <c r="P35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>Must not graduate before the end of the REU.</t>
+        </is>
+      </c>
       <c r="Q35" s="2" t="inlineStr"/>
       <c r="R35" s="2" t="inlineStr"/>
       <c r="S35" s="2" t="inlineStr"/>
       <c r="T35" s="2" t="inlineStr"/>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen or permanent resident | Undergraduates; current REU eligibility rules apply</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="inlineStr"/>
+          <t>U.S. citizen or permanent resident; active undergraduate at a U.S. or foreign university; must not graduate before the end of the program. The program primarily admits juniors, some exceptional sophomores, and does not usually admit first-years.</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>Junior/sophomore/first-year language is selection preference rather than a hard exclusion; no other job or summer-class commitment allowed.</t>
+        </is>
+      </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -14757,26 +16325,66 @@
           <t>U.S. citizen or permanent resident</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Undergraduates enrolled at U.S. institutions; see current cycle</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P36" s="2" t="inlineStr"/>
       <c r="Q36" s="2" t="inlineStr"/>
       <c r="R36" s="2" t="inlineStr"/>
       <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -14784,13 +16392,13 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Yes | U.S. citizen or permanent resident | Undergraduates enrolled at U.S. institutions; see current cycle</t>
+          <t>U.S. citizen or permanent resident currently enrolled in an undergraduate degree program at a U.S. college or university.</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr"/>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>needs_review</t>
+          <t>reviewed</t>
         </is>
       </c>
     </row>
@@ -14808,7 +16416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -14915,12 +16523,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://science.osti.gov/wdts/suli</t>
+          <t>https://btaa.org/resources-for/students/srop/eligibility</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DOE Office of Science</t>
+          <t>Big Ten SROP – University of Iowa eligibility</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -14943,17 +16551,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://science.osti.gov/wdts/suli/how-to-apply</t>
+          <t>https://science.osti.gov/wdts/suli</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Science Undergraduate Laboratory Internships (SULI) application</t>
+          <t>DOE Office of Science</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>official_application</t>
+          <t>official_program</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -14971,17 +16579,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://www.training.nih.gov/research-training/pb/sip/</t>
+          <t>https://science.osti.gov/wdts/suli/how-to-apply</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>NIH Summer Internship Program (SIP) application</t>
+          <t>Science Undergraduate Laboratory Internships (SULI) application</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>official_program</t>
+          <t>official_application</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -14999,12 +16607,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://www.nasa.gov/learning-resources/internship-programs/</t>
+          <t>https://science.osti.gov/wdts/suli/Eligibility</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>NASA OSTEM</t>
+          <t>Science Undergraduate Laboratory Internships (SULI) eligibility</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -15027,17 +16635,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://www.stemgateway.nasa.gov/</t>
+          <t>https://www.training.nih.gov/research-training/pb/sip/</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>NASA OSTEM Internship Program application</t>
+          <t>NIH Summer Internship Program (SIP) application</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>official_application</t>
+          <t>official_program</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -15055,12 +16663,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://www.nist.gov/surf</t>
+          <t>https://www.nasa.gov/learning-resources/internship-programs/</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>NIST Summer Undergraduate Research Fellowship (SURF) application</t>
+          <t>NASA OSTEM</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -15083,17 +16691,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>https://www.onr.navy.mil/education-outreach/undergraduate-graduate/nreip-naval-internship</t>
+          <t>https://www.stemgateway.nasa.gov/</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Naval Research Enterprise Internship Program (NREIP) application</t>
+          <t>NASA OSTEM Internship Program application</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>official_program</t>
+          <t>official_application</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -15111,12 +16719,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>https://www.daad.de/rise/en/rise-germany/</t>
+          <t>https://www.nasa.gov/learning-resources/internship-programs/intern-frequently-asked-questions/</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>DAAD RISE Germany</t>
+          <t>NASA OSTEM Internship Program eligibility</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -15139,17 +16747,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://www.daad.de/rise/en/rise-germany/find-an-internship/what-applicants-need-to-know/</t>
+          <t>https://www.nist.gov/surf</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>RISE Germany application</t>
+          <t>NIST Summer Undergraduate Research Fellowship (SURF) application</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>official_application</t>
+          <t>official_program</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -15167,12 +16775,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://theleadershipalliance.org/summer-research-early-identification-program</t>
+          <t>https://www.onr.navy.mil/education-outreach/undergraduate-graduate/nreip-naval-internship</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>The Leadership Alliance</t>
+          <t>Naval Research Enterprise Internship Program (NREIP) application</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -15195,17 +16803,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>https://app.theleadershipalliance.org/</t>
+          <t>https://www.daad.de/rise/en/rise-germany/</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Summer Research Early Identification Program (SR-EIP) application</t>
+          <t>DAAD RISE Germany</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>official_application</t>
+          <t>official_program</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -15223,17 +16831,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>https://www.med.upenn.edu/research-trainee-affairs/suip/</t>
+          <t>https://www.daad.de/rise/en/rise-germany/find-an-internship/what-applicants-need-to-know/</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Summer Undergraduate Internship Program (SUIP) application</t>
+          <t>RISE Germany application</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>official_program</t>
+          <t>official_application</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -15251,12 +16859,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>https://www.rockefeller.edu/education-and-training/surf/application-information/</t>
+          <t>https://theleadershipalliance.org/summer-research-early-identification-program</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>University program</t>
+          <t>The Leadership Alliance</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -15279,12 +16887,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>https://surfapplication.rockefeller.edu/</t>
+          <t>https://app.theleadershipalliance.org/</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Summer Undergraduate Research Fellowship (SURF) application</t>
+          <t>Summer Research Early Identification Program (SR-EIP) application</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -15307,12 +16915,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>https://www.cshl.edu/education/undergraduate-research-program/</t>
+          <t>https://www.med.upenn.edu/research-trainee-affairs/suip/</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Undergraduate Research Program (URP) application</t>
+          <t>Summer Undergraduate Internship Program (SUIP) application</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -15335,12 +16943,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>https://www.fredhutch.org/en/education-training/undergraduate-students/summer-undergraduate-research-program.html</t>
+          <t>https://www.rockefeller.edu/education-and-training/surf/application-information/</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Summer Undergraduate Research Program (SURP) application</t>
+          <t>University program</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -15363,17 +16971,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>https://www.fredhutch.org/en/education-training/undergraduate-students/pathways-undergraduate-researchers.html</t>
+          <t>https://surfapplication.rockefeller.edu/</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Pathways Undergraduate Researchers application</t>
+          <t>Summer Undergraduate Research Fellowship (SURF) application</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>official_program</t>
+          <t>official_application</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -15391,12 +16999,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>https://www.fredhutch.org/en/education-training/undergraduate-students/seattlestatgrows.html</t>
+          <t>https://www.cshl.edu/education/undergraduate-research-program/</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>SeattleStatGROWS application</t>
+          <t>Undergraduate Research Program (URP) application</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -15419,12 +17027,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/surf/</t>
+          <t>https://www.fredhutch.org/en/education-training/undergraduate-students/summer-undergraduate-research-program.html</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>NSF REU / university program</t>
+          <t>Summer Undergraduate Research Program (SURP) application</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -15447,17 +17055,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>https://etap.nsf.gov/</t>
+          <t>https://www.fredhutch.org/en/education-training/undergraduate-students/pathways-undergraduate-researchers.html</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Boston University SURF / REU application</t>
+          <t>Pathways Undergraduate Researchers application</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>official_application</t>
+          <t>official_program</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -15475,12 +17083,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>https://sites.bu.edu/physics-resources/physics-reu/</t>
+          <t>https://www.fredhutch.org/en/education-training/undergraduate-students/seattlestatgrows.html</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>BU Physics Research Opportunities (BU-PRO) application</t>
+          <t>SeattleStatGROWS application</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -15503,7 +17111,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/photonics-programs/reu/programs/</t>
+          <t>https://www.bu.edu/surf/</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -15531,12 +17139,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>https://www.bu.edu/photonics-programs/reu/apply/</t>
+          <t>https://etap.nsf.gov/</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Integrated Nanomanufacturing REU application</t>
+          <t>Boston University SURF / REU application</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -15559,12 +17167,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>https://amgenscholars.berkeley.edu/</t>
+          <t>https://sites.bu.edu/physics-resources/physics-reu/</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Amgen Scholars</t>
+          <t>BU Physics Research Opportunities (BU-PRO) application</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -15587,17 +17195,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>https://amgenscholars.berkeley.edu/applicants/</t>
+          <t>https://sites.bu.edu/physics-resources/physics-reu/about-the-program/</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Amgen Scholars Program at UC Berkeley application</t>
+          <t>BU Physics Research Opportunities (BU-PRO) eligibility</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>official_application</t>
+          <t>official_program</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -15615,12 +17223,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>https://biosciences.stanford.edu/pathways/ssrp-amgen-scholars-program/</t>
+          <t>https://www.bu.edu/photonics-programs/reu/programs/</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Amgen Scholars</t>
+          <t>NSF REU / university program</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -15643,12 +17251,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>https://biosciences.stanford.edu/pathways/ssrp-amgen-scholars-program/the-ssrp-amgen-scholars-program-application/</t>
+          <t>https://www.bu.edu/photonics-programs/reu/apply/</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Stanford SSRP-Amgen Scholars Program application</t>
+          <t>Integrated Nanomanufacturing REU application</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -15671,12 +17279,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>https://uraf.harvard.edu/amgen-scholars</t>
+          <t>https://amgenscholars.berkeley.edu/</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Harvard Amgen Scholars Program application</t>
+          <t>Amgen Scholars</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -15699,17 +17307,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>https://harvardforest.fas.harvard.edu/education-opportunities/undergraduate-students/summer-research-program/summer-research-program-information-for-students/</t>
+          <t>https://amgenscholars.berkeley.edu/applicants/</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Harvard Forest Summer Research Program in Ecology application</t>
+          <t>Amgen Scholars Program at UC Berkeley application</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>official_program</t>
+          <t>official_application</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -15727,12 +17335,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>https://www.ipam.ucla.edu/programs/student-research-programs/research-in-industrial-projects-for-students-rips-2026-los-angeles/</t>
+          <t>https://biosciences.stanford.edu/pathways/ssrp-amgen-scholars-program/</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Research in Industrial Projects for Students (RIPS-LA) application</t>
+          <t>Amgen Scholars</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -15755,17 +17363,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>https://reu.dimacs.rutgers.edu/</t>
+          <t>https://biosciences.stanford.edu/pathways/ssrp-amgen-scholars-program/the-ssrp-amgen-scholars-program-application/</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>DIMACS REU application</t>
+          <t>Stanford SSRP-Amgen Scholars Program application</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>official_program</t>
+          <t>official_application</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -15783,12 +17391,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>https://cos.gatech.edu/qbiosreu</t>
+          <t>https://biosciences.stanford.edu/pathways/ssrp-amgen-scholars-program/criteria-and-application-requirements/</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Quantitative Biosciences Undergraduate Summer Research Experience (QBioS REU) application</t>
+          <t>Stanford SSRP-Amgen Scholars Program eligibility</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -15798,6 +17406,202 @@
       </c>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>https://uraf.harvard.edu/amgen-scholars</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Harvard Amgen Scholars Program application</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>official_program</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>https://harvardforest.fas.harvard.edu/education-opportunities/undergraduate-students/summer-research-program/summer-research-program-information-for-students/</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Harvard Forest Summer Research Program in Ecology application</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>official_program</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ipam.ucla.edu/programs/student-research-programs/research-in-industrial-projects-for-students-rips-2026-los-angeles/</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Research in Industrial Projects for Students (RIPS-LA) application</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>official_program</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ipam.ucla.edu/programs/student-research-programs/research-in-industrial-projects-for-students-rips-2026-los-angeles/?tab=faq</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Research in Industrial Projects for Students (RIPS-LA) eligibility</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>official_program</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>https://reu.dimacs.rutgers.edu/</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>DIMACS REU application</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>official_program</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>https://dimacs.rutgers.edu/apply-to-the-dimacs-reu</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>DIMACS REU eligibility</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>official_program</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>https://cos.gatech.edu/qbiosreu</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Quantitative Biosciences Undergraduate Summer Research Experience (QBioS REU) application</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>official_program</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -15817,7 +17621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -15828,7 +17632,7 @@
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
@@ -15893,7 +17697,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -15908,28 +17712,28 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>partially_verified</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>seed_dataset</t>
+          <t>OpenAI Codex; official program source</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -15938,7 +17742,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -15953,7 +17757,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -15968,7 +17772,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>["Application_URL"]</t>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Degree_Seeking_Required", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -15983,24 +17787,24 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>2026-08-31</t>
@@ -16013,7 +17817,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["Application_URL"]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -16028,7 +17832,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -16043,28 +17847,28 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>partially_verified</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>["Application_URL"]</t>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>seed_dataset</t>
+          <t>OpenAI Codex; official program source</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -16073,17 +17877,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -16103,7 +17907,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Degree_Seeking_Required", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -16118,17 +17922,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -16163,43 +17967,43 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>partially_verified</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>seed_dataset</t>
+          <t>OpenAI Codex; official program source</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -16208,22 +18012,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -16238,7 +18042,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>["Application_URL"]</t>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Degree_Seeking_Required", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -16253,22 +18057,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -16283,7 +18087,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["Application_URL"]</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -16298,43 +18102,43 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>partially_verified</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>["Application_URL"]</t>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>seed_dataset</t>
+          <t>OpenAI Codex; official program source</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -16343,17 +18147,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -16373,7 +18177,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Degree_Seeking_Required", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -16388,17 +18192,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -16433,43 +18237,43 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>partially_verified</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>seed_dataset</t>
+          <t>OpenAI Codex; official program source</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -16478,22 +18282,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -16508,7 +18312,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>["Application_URL"]</t>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Degree_Seeking_Required", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
@@ -16523,22 +18327,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -16553,7 +18357,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["Application_URL"]</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
@@ -16568,43 +18372,43 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>partially_verified</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>["Application_URL"]</t>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>seed_dataset</t>
+          <t>OpenAI Codex; official program source</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -16613,17 +18417,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -16643,7 +18447,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Degree_Seeking_Required", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -16658,17 +18462,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -16703,43 +18507,43 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>partially_verified</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>seed_dataset</t>
+          <t>OpenAI Codex; official program source</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -16748,22 +18552,22 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -16778,7 +18582,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>["Application_URL"]</t>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Degree_Seeking_Required", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -16793,22 +18597,22 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -16823,7 +18627,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["Application_URL"]</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -16838,43 +18642,43 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>partially_verified</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>["Application_URL"]</t>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>seed_dataset</t>
+          <t>OpenAI Codex; official program source</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
@@ -16883,17 +18687,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -16913,7 +18717,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Degree_Seeking_Required", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
@@ -16928,17 +18732,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -16973,17 +18777,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -16993,23 +18797,23 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>partially_verified</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>seed_dataset</t>
+          <t>OpenAI Codex; official program source</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -17018,22 +18822,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -17048,7 +18852,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>["Application_URL"]</t>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Degree_Seeking_Required", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
@@ -17063,22 +18867,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -17093,7 +18897,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Deadline_Text", "Cycle_Year", "Status", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["Application_URL"]</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -17108,43 +18912,43 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>partially_verified</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>seed_dataset</t>
+          <t>OpenAI Codex; official program source</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -17153,22 +18957,22 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -17183,7 +18987,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>["Application_URL"]</t>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Degree_Seeking_Required", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -17198,22 +19002,22 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -17228,7 +19032,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["Application_URL"]</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -17243,43 +19047,43 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>partially_verified</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>seed_dataset</t>
+          <t>OpenAI Codex; official program source</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
@@ -17288,22 +19092,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -17318,7 +19122,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Degree_Seeking_Required", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
@@ -17333,22 +19137,22 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -17378,43 +19182,43 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>partially_verified</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>seed_dataset</t>
+          <t>OpenAI Codex; official program source</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -17423,22 +19227,22 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -17453,7 +19257,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>["Application_URL"]</t>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Degree_Seeking_Required", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -17468,22 +19272,22 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -17498,7 +19302,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["Application_URL"]</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
@@ -17513,43 +19317,43 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>partially_verified</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>seed_dataset</t>
+          <t>OpenAI Codex; official program source</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
@@ -17558,22 +19362,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -17588,7 +19392,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>["Application_URL"]</t>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Two_Year_Institution_Eligible", "Four_Year_Institution_Eligible", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
@@ -17603,22 +19407,22 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -17633,7 +19437,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["Application_URL"]</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -17648,43 +19452,43 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>partially_verified</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>seed_dataset</t>
+          <t>OpenAI Codex; official program source</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
@@ -17693,22 +19497,22 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -17723,7 +19527,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Deadline_Text", "Cycle_Year", "Status", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Deadline_Text", "Cycle_Year", "Status", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Two_Year_Institution_Eligible", "Four_Year_Institution_Eligible", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -17738,43 +19542,43 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>partially_verified</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>seed_dataset</t>
+          <t>OpenAI Codex; official program source</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -17783,22 +19587,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -17813,7 +19617,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Degree_Seeking_Required", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
@@ -17828,22 +19632,22 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -17873,43 +19677,43 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>partially_verified</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>seed_dataset</t>
+          <t>OpenAI Codex; official program source</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -17918,22 +19722,22 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -17948,7 +19752,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Two_Year_Institution_Eligible", "Four_Year_Institution_Eligible", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -17963,43 +19767,43 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>partially_verified</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>["Application_URL"]</t>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>seed_dataset</t>
+          <t>OpenAI Codex; official program source</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -18008,22 +19812,22 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -18038,7 +19842,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -18053,43 +19857,43 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>partially_verified</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>["Application_URL"]</t>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>seed_dataset</t>
+          <t>OpenAI Codex; official program source</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -18098,22 +19902,22 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -18128,7 +19932,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Four_Year_Institution_Eligible", "Degree_Seeking_Required", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
@@ -18143,22 +19947,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -18188,43 +19992,43 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>partially_verified</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>seed_dataset</t>
+          <t>OpenAI Codex; official program source</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -18233,22 +20037,22 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -18263,7 +20067,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Degree_Seeking_Required", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -18278,22 +20082,22 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -18308,7 +20112,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["Application_URL"]</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -18323,43 +20127,43 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>partially_verified</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>seed_dataset</t>
+          <t>OpenAI Codex; official program source</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
@@ -18368,22 +20172,22 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -18398,7 +20202,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes"]</t>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "Sophomore_Eligible", "Junior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Two_Year_Institution_Eligible", "Four_Year_Institution_Eligible", "Degree_Seeking_Required", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -18409,6 +20213,1491 @@
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI Codex; official program source</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>partially_verified</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Prior_Research_Status", "Raw_Eligibility_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>seed_dataset</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>partially_verified</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>["Application_URL"]</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>seed_dataset</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI Codex; official program source</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>partially_verified</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Degree_Seeking_Required", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>seed_dataset</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI Codex; official program source</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>partially_verified</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Prior_Research_Status", "Raw_Eligibility_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>seed_dataset</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI Codex; official program source</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>partially_verified</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Deadline_Text", "Cycle_Year", "Status", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Two_Year_Institution_Eligible", "Four_Year_Institution_Eligible", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>seed_dataset</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI Codex; official program source</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>partially_verified</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Two_Year_Institution_Eligible", "Four_Year_Institution_Eligible", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>seed_dataset</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI Codex; official program source</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>partially_verified</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Sophomore_Eligible", "Junior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>seed_dataset</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>partially_verified</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>["Application_URL"]</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>seed_dataset</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI Codex; official program source</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>partially_verified</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "Enrolled_Required", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>seed_dataset</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI Codex; official program source</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>partially_verified</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Two_Year_Institution_Eligible", "Four_Year_Institution_Eligible", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>seed_dataset</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>partially_verified</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>["Application_URL"]</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>seed_dataset</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>partially_verified</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Institution_Type_Rule_Text", "Two_Year_Institution_Eligible", "Four_Year_Institution_Eligible", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>seed_dataset</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>["Application_URL", "eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>codex_official_source_review</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>partially_verified</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Min_GPA", "Duration_Weeks", "Program_Start", "Program_End", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Institution_Type_Rule_Text", "Two_Year_Institution_Eligible", "Four_Year_Institution_Eligible", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>seed_dataset</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>partially_verified</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>["Application_URL"]</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>seed_dataset</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>codex_official_source_review</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>["Academic_Credit", "Application_Deadline", "Citizenship", "Citizenship_International", "Citizenship_Permanent_Resident", "Citizenship_US_Citizen", "City", "Country", "Cycle_Year", "Data_Confidence", "Deadline_Text", "Duration_Weeks", "Eligibility_Checked_By", "Eligibility_Checked_On", "Eligibility_Parse_Status", "Eligibility_Source_URL", "Eligible_Years", "Enrolled_Required", "External_Applicants", "Field_Tags", "First_Year_Eligible", "Format", "Four_Year_Institution_Eligible", "Graduating_Senior_Eligible", "Graduation_Rule_Text", "Host_Institution", "Housing_Details", "Housing_Included", "Institution_Type_Rule_Text", "Junior_Eligible", "Last_Verified", "Location_Scope", "Meals_Details", "Meals_Included", "Min_GPA", "Network_Source", "Notes", "Other_Rule_Text", "Primary_Field", "Prior_Research_Status", "Program_End", "Program_ID", "Program_Name", "Program_Start", "Program_Type", "Program_URL", "Raw_Eligibility_Text", "Senior_Eligible", "Sophomore_Eligible", "State", "Status", "Travel_Details", "Travel_Included", "Two_Year_Institution_Eligible", "eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>codex_official_source_review</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI Codex; official program source</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>partially_verified</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Application_Open", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Two_Year_Institution_Eligible", "Four_Year_Institution_Eligible", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>seed_dataset</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI Codex; official program source</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>partially_verified</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Two_Year_Institution_Eligible", "Four_Year_Institution_Eligible", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>seed_dataset</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI Codex; official program source</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>partially_verified</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Program_Start", "Program_End", "Application_Deadline", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Graduation_Rule_Text", "Prior_Research_Status", "Raw_Eligibility_Text", "Other_Rule_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>seed_dataset</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>["eligibility_rules.citizenship_international", "eligibility_rules.citizenship_permanent_resident", "eligibility_rules.citizenship_rule_text", "eligibility_rules.citizenship_us_citizen", "eligibility_rules.degree_seeking_required", "eligibility_rules.eligible_years_text", "eligibility_rules.enrolled_required", "eligibility_rules.external_applicants_status", "eligibility_rules.first_year_eligible", "eligibility_rules.four_year_institution_eligible", "eligibility_rules.graduating_senior_eligible", "eligibility_rules.graduation_rule_text", "eligibility_rules.institution_type_rule_text", "eligibility_rules.junior_eligible", "eligibility_rules.min_gpa", "eligibility_rules.other_rule_text", "eligibility_rules.parse_status", "eligibility_rules.prior_research_status", "eligibility_rules.raw_eligibility_text", "eligibility_rules.senior_eligible", "eligibility_rules.sophomore_eligible", "eligibility_rules.two_year_institution_eligible"]</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI Codex; official program source</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>partially_verified</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>["Program_ID", "Program_Name", "Host_Institution", "Network_Source", "Program_Type", "Primary_Field", "Field_Tags", "City", "State", "Country", "Location_Scope", "Format", "External_Applicants", "Citizenship", "Eligible_Years", "Duration_Weeks", "Deadline_Text", "Cycle_Year", "Status", "Stipend_Total_USD", "Stipend_Weekly_USD", "Housing_Included", "Housing_Details", "Meals_Included", "Meals_Details", "Travel_Included", "Travel_Details", "Academic_Credit", "Program_URL", "Last_Verified", "Data_Confidence", "Notes", "Eligibility_Parse_Status", "Citizenship_US_Citizen", "Citizenship_Permanent_Resident", "Citizenship_International", "First_Year_Eligible", "Sophomore_Eligible", "Junior_Eligible", "Senior_Eligible", "Graduating_Senior_Eligible", "Enrolled_Required", "Degree_Seeking_Required", "Prior_Research_Status", "Raw_Eligibility_Text", "Eligibility_Source_URL", "Eligibility_Checked_On", "Eligibility_Checked_By"]</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>seed_dataset</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
